--- a/proliferation_growth_curves/Incucyte_sheets/processed/r7_processed.xlsx
+++ b/proliferation_growth_curves/Incucyte_sheets/processed/r7_processed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/allielas/HTP_fibroblasts_mitolyso/proliferation_growth_curves/Incucyte_sheets/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBBE596-D1C9-7D43-85F0-33668A53584B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64353FCC-B0EC-0440-BDD3-D54D0CC4FC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33380" yWindow="-2040" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="900" windowWidth="29100" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Averages" sheetId="1" r:id="rId1"/>
@@ -296,23 +296,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -352,6 +340,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -659,86 +650,86 @@
   <dimension ref="A1:AB40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:28" s="16" customFormat="1" ht="68" x14ac:dyDescent="0.2">
-      <c r="B1" s="17" t="s">
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="20" t="s">
+      <c r="I1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="M1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="O1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="P1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="24" t="s">
+      <c r="Q1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="24" t="s">
+      <c r="R1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="25" t="s">
+      <c r="S1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="25" t="s">
+      <c r="T1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="26" t="s">
+      <c r="U1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="26" t="s">
+      <c r="V1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="27" t="s">
+      <c r="W1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="27" t="s">
+      <c r="X1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="28" t="s">
+      <c r="Y1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="28" t="s">
+      <c r="Z1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="17" t="s">
+      <c r="AA1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="17" t="s">
+      <c r="AB1" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -791,10 +782,10 @@
       <c r="P2">
         <v>10.800267</v>
       </c>
-      <c r="Q2" s="14">
+      <c r="Q2" s="2">
         <v>12.947817875</v>
       </c>
-      <c r="R2" s="14">
+      <c r="R2" s="2">
         <v>10.32589475</v>
       </c>
       <c r="S2">
@@ -3753,17 +3744,17 @@
       </c>
     </row>
     <row r="40" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="E40" s="15"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="14"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3775,50 +3766,50 @@
   <dimension ref="A1:AB36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="17" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4121,17 +4112,17 @@
       <c r="P7">
         <v>0.42110420625</v>
       </c>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
-      <c r="AB7" s="14"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2"/>
     </row>
     <row r="8" spans="1:28" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
@@ -4182,47 +4173,47 @@
       <c r="P8">
         <v>0.15880235500000001</v>
       </c>
-      <c r="R8" s="15" t="str">
+      <c r="R8" s="3" t="str">
         <f>_xlfn.CONCAT(R1," ",R7)</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="S8" s="14" t="str">
+      <c r="S8" s="2" t="str">
         <f>_xlfn.CONCAT(S1," ",S7)</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="T8" s="14" t="str">
+      <c r="T8" s="2" t="str">
         <f>_xlfn.CONCAT(T1," ",T7)</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="U8" s="14" t="str">
+      <c r="U8" s="2" t="str">
         <f>_xlfn.CONCAT(U1," ",U7)</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="V8" s="15" t="str">
+      <c r="V8" s="3" t="str">
         <f>_xlfn.CONCAT(V1," ",V7)</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="W8" s="15" t="str">
+      <c r="W8" s="3" t="str">
         <f>_xlfn.CONCAT(W1," ",W7)</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="X8" s="14" t="str">
+      <c r="X8" s="2" t="str">
         <f>_xlfn.CONCAT(X1," ",X7)</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Y8" s="14" t="str">
+      <c r="Y8" s="2" t="str">
         <f>_xlfn.CONCAT(Y1," ",Y7)</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z8" s="15" t="str">
+      <c r="Z8" s="3" t="str">
         <f>_xlfn.CONCAT(Z1," ",Z7)</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AA8" s="14" t="str">
+      <c r="AA8" s="2" t="str">
         <f>_xlfn.CONCAT(AA1," ",AA7)</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AB8" s="14" t="str">
+      <c r="AB8" s="2" t="str">
         <f>_xlfn.CONCAT(AB1," ",AB7)</f>
         <v xml:space="preserve"> </v>
       </c>
